--- a/grupos/5ARHM - Estadisticos 20211.xlsx
+++ b/grupos/5ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -152,18 +152,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -179,172 +179,172 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>TEHUINTLE</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
   </si>
   <si>
     <t>ALAMILLO</t>
   </si>
   <si>
-    <t>MARCELINO</t>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>YATZIRI NAOMI</t>
   </si>
   <si>
+    <t>HANNIA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ISMERAI</t>
+  </si>
+  <si>
+    <t>DAMARIS JABNEL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FERNANDA CAMILA</t>
+  </si>
+  <si>
     <t>NURIEL</t>
   </si>
   <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
+    <t>MELISSA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CATHERIN DALAY</t>
+  </si>
+  <si>
+    <t>ALMA EDITH</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>KATHE ALONDRA</t>
   </si>
   <si>
     <t>DANIELA</t>
   </si>
   <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
     <t>CRISTINA</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>HANNIA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISMERAI</t>
-  </si>
-  <si>
-    <t>DAMARIS JABNEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FERNANDA CAMILA</t>
-  </si>
-  <si>
-    <t>MELISSA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CATHERIN DALAY</t>
-  </si>
-  <si>
-    <t>ALMA EDITH</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
-    <t>KATHE ALONDRA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
   <si>
     <t>RENATA</t>
@@ -839,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -857,10 +857,10 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -893,7 +893,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -934,10 +934,10 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -973,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1011,10 +1011,10 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1050,7 +1050,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1088,10 +1088,10 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1165,10 +1165,10 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1201,10 +1201,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1242,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1319,10 +1319,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1355,10 +1355,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1396,10 +1396,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1432,10 +1432,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1473,10 +1473,10 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1550,10 +1550,10 @@
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1627,10 +1627,10 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1704,10 +1704,10 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1740,7 +1740,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1781,10 +1781,10 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1817,10 +1817,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1858,10 +1858,10 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1897,7 +1897,7 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1935,10 +1935,10 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -1971,10 +1971,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -1997,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2012,10 +2012,10 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2051,7 +2051,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2074,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2089,10 +2089,10 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2125,10 +2125,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2151,7 +2151,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2205,7 +2205,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2243,10 +2243,10 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2279,10 +2279,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2320,10 +2320,10 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2356,10 +2356,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2382,7 +2382,7 @@
         <v>-1</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2400,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2436,7 +2436,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2474,10 +2474,10 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2551,10 +2551,10 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -2667,30 +2667,30 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>21.74</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -2699,33 +2699,33 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>91.3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>9.5</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>86.95999999999999</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>8.699999999999999</v>
-      </c>
-      <c r="H3">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>4.35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -2734,22 +2734,22 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>91.3</v>
       </c>
       <c r="G4">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>9.5</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2757,57 +2757,57 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>23</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G6">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2855,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2884,59 +2884,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920125</v>
+        <v>19330051920133</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920131</v>
+        <v>19330051920140</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
         <v>60</v>
       </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920133</v>
+        <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>45</v>
@@ -2944,142 +2944,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" t="s">
         <v>61</v>
       </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920140</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920145</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920145</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3118,47 +2998,47 @@
         <v>19330051920145</v>
       </c>
       <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920140</v>
+        <v>19330051920133</v>
       </c>
       <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920125</v>
+        <v>19330051920140</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3166,81 +3046,81 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920131</v>
+        <v>19330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920133</v>
+        <v>19330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920139</v>
+        <v>19330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920141</v>
+        <v>19330051920128</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920126</v>
+        <v>19330051920129</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>96</v>
@@ -3251,13 +3131,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920127</v>
+        <v>19330051920130</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>97</v>
@@ -3268,13 +3148,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920128</v>
+        <v>19330051920380</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>
@@ -3285,13 +3165,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920129</v>
+        <v>19330051920131</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -3302,13 +3182,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920130</v>
+        <v>19330051920132</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -3319,13 +3199,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920380</v>
+        <v>19330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>101</v>
@@ -3336,13 +3216,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920132</v>
+        <v>19330051920135</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>102</v>
@@ -3353,13 +3233,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920134</v>
+        <v>19330051920002</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3370,13 +3250,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920135</v>
+        <v>19330051920136</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
         <v>104</v>
@@ -3387,13 +3267,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920002</v>
+        <v>19330051920137</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>105</v>
@@ -3404,13 +3284,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920136</v>
+        <v>19330051920139</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>106</v>
@@ -3421,13 +3301,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920137</v>
+        <v>19330051920143</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
@@ -3438,13 +3318,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920143</v>
+        <v>19330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
         <v>108</v>
@@ -3458,10 +3338,10 @@
         <v>19330051920144</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -3475,10 +3355,10 @@
         <v>19330051920147</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
         <v>110</v>
@@ -3492,10 +3372,10 @@
         <v>19330051920431</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
         <v>111</v>
@@ -3511,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3546,19 +3426,19 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3569,19 +3449,19 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3589,19 +3469,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920140</v>
+        <v>19330051920133</v>
       </c>
       <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -3615,136 +3495,21 @@
         <v>19330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920125</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920131</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920141</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5ARHM - Estadisticos 20211.xlsx
+++ b/grupos/5ARHM - Estadisticos 20211.xlsx
@@ -869,10 +869,10 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -905,10 +905,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -943,13 +943,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1020,13 +1020,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1097,13 +1097,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1139,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1174,13 +1174,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1213,10 +1213,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1328,13 +1328,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1405,13 +1405,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1482,13 +1482,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1636,13 +1636,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1675,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1713,13 +1713,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1752,7 +1752,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1790,13 +1790,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1832,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1867,13 +1867,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1944,13 +1944,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2024,10 +2024,10 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2060,10 +2060,10 @@
         <v>-1</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2098,13 +2098,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2134,13 +2134,13 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2181,7 +2181,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2252,13 +2252,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2329,13 +2329,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2409,10 +2409,10 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2483,13 +2483,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2563,10 +2563,10 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2599,10 +2599,10 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2679,7 +2679,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I3">
         <v>2</v>

--- a/grupos/5ARHM - Estadisticos 20211.xlsx
+++ b/grupos/5ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -152,21 +152,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -179,148 +179,148 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
+    <t>JARED JESUS</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>HANNIA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ISMERAI</t>
+  </si>
+  <si>
+    <t>DAMARIS JABNEL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FERNANDA CAMILA</t>
+  </si>
+  <si>
+    <t>NURIEL</t>
+  </si>
+  <si>
+    <t>MELISSA MONSERRAT</t>
   </si>
   <si>
     <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>HANNIA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISMERAI</t>
-  </si>
-  <si>
-    <t>DAMARIS JABNEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FERNANDA CAMILA</t>
-  </si>
-  <si>
-    <t>NURIEL</t>
-  </si>
-  <si>
-    <t>MELISSA MONSERRAT</t>
   </si>
   <si>
     <t>ITZEL</t>
@@ -863,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -899,7 +899,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -940,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1017,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1094,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1207,7 +1207,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1284,7 +1284,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1361,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1402,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1479,7 +1479,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1515,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1547,7 +1547,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>7</v>
@@ -1556,16 +1556,16 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1601,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1633,7 +1633,7 @@
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -1710,7 +1710,7 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -1787,7 +1787,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1864,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>9</v>
@@ -1941,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -1977,7 +1977,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2054,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>8</v>
@@ -2131,7 +2131,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2172,7 +2172,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2249,7 +2249,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>10</v>
@@ -2326,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -2362,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2403,7 +2403,7 @@
         <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>-1</v>
@@ -2480,7 +2480,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -2557,7 +2557,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2593,7 +2593,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -2667,25 +2667,25 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>86.95999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="G2">
-        <v>8.699999999999999</v>
+        <v>17.39</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -2743,7 +2743,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
@@ -2763,30 +2763,30 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>95.65000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
@@ -2798,27 +2798,27 @@
         <v>22</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>95.65000000000001</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>4.35</v>
-      </c>
-      <c r="H6">
-        <v>7.6</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -2827,19 +2827,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2855,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2884,36 +2884,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920133</v>
+        <v>19330051920140</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920140</v>
+        <v>19330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -2927,39 +2927,19 @@
         <v>19330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
         <v>58</v>
       </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920145</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2998,13 +2978,13 @@
         <v>19330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3012,16 +2992,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920133</v>
+        <v>19330051920140</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3029,30 +3009,30 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920140</v>
+        <v>19330051920125</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920125</v>
+        <v>19330051920126</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
         <v>92</v>
@@ -3063,10 +3043,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920126</v>
+        <v>19330051920127</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
         <v>79</v>
@@ -3080,10 +3060,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920127</v>
+        <v>19330051920128</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
@@ -3097,13 +3077,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920128</v>
+        <v>19330051920129</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>95</v>
@@ -3114,13 +3094,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920129</v>
+        <v>19330051920130</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>96</v>
@@ -3131,10 +3111,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920130</v>
+        <v>19330051920380</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
@@ -3148,10 +3128,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920380</v>
+        <v>19330051920131</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
@@ -3165,13 +3145,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920131</v>
+        <v>19330051920132</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -3182,13 +3162,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920132</v>
+        <v>19330051920133</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -3202,10 +3182,10 @@
         <v>19330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
         <v>101</v>
@@ -3219,10 +3199,10 @@
         <v>19330051920135</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>102</v>
@@ -3236,10 +3216,10 @@
         <v>19330051920002</v>
       </c>
       <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
         <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3253,10 +3233,10 @@
         <v>19330051920136</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>104</v>
@@ -3270,10 +3250,10 @@
         <v>19330051920137</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>105</v>
@@ -3287,10 +3267,10 @@
         <v>19330051920139</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>106</v>
@@ -3304,10 +3284,10 @@
         <v>19330051920143</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
@@ -3321,10 +3301,10 @@
         <v>19330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>108</v>
@@ -3338,10 +3318,10 @@
         <v>19330051920144</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -3355,10 +3335,10 @@
         <v>19330051920147</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
         <v>110</v>
@@ -3372,10 +3352,10 @@
         <v>19330051920431</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
         <v>111</v>
@@ -3391,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3426,19 +3406,19 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3449,19 +3429,19 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3469,25 +3449,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920133</v>
+        <v>19330051920140</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3495,13 +3475,13 @@
         <v>19330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
         <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3511,6 +3491,52 @@
       </c>
       <c r="G5">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920139</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ARHM - Estadisticos 20211.xlsx
+++ b/grupos/5ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -152,21 +152,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -179,175 +179,175 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SOLIS</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>HANNIA MONSERRAT</t>
+  </si>
+  <si>
+    <t>ISMERAI</t>
+  </si>
+  <si>
+    <t>DAMARIS JABNEL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FERNANDA CAMILA</t>
+  </si>
+  <si>
+    <t>NURIEL</t>
+  </si>
+  <si>
+    <t>MELISSA MONSERRAT</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CATHERIN DALAY</t>
+  </si>
+  <si>
+    <t>ALMA EDITH</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>KATHE ALONDRA</t>
+  </si>
+  <si>
     <t>MARLENE ALICIA</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>CRISTINA</t>
+  </si>
+  <si>
+    <t>RENATA</t>
+  </si>
+  <si>
     <t>JARED JESUS</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>HANNIA MONSERRAT</t>
-  </si>
-  <si>
-    <t>ISMERAI</t>
-  </si>
-  <si>
-    <t>DAMARIS JABNEL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FERNANDA CAMILA</t>
-  </si>
-  <si>
-    <t>NURIEL</t>
-  </si>
-  <si>
-    <t>MELISSA MONSERRAT</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CATHERIN DALAY</t>
-  </si>
-  <si>
-    <t>ALMA EDITH</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
-    <t>KATHE ALONDRA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>CRISTINA</t>
-  </si>
-  <si>
-    <t>RENATA</t>
   </si>
   <si>
     <t>ABRIL</t>
@@ -866,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -875,22 +875,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -899,16 +899,16 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -952,22 +952,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1029,25 +1029,25 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1106,25 +1106,25 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1136,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1183,22 +1183,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1213,10 +1213,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1251,49 +1251,49 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1337,31 +1337,31 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1414,25 +1414,25 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1491,25 +1491,25 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1568,25 +1568,25 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1601,7 +1601,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1645,28 +1645,28 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1722,25 +1722,25 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1799,22 +1799,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1832,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1876,22 +1876,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1900,13 +1900,13 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1953,25 +1953,25 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2003,7 +2003,7 @@
         <v>6</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -2021,7 +2021,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2030,22 +2030,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2054,16 +2054,16 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2107,40 +2107,40 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2175,34 +2175,34 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2211,13 +2211,13 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2261,25 +2261,25 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2338,22 +2338,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2379,7 +2379,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2388,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2397,7 +2397,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2406,7 +2406,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2415,25 +2415,25 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2442,7 +2442,7 @@
         <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2492,40 +2492,40 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2560,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -2569,40 +2569,40 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
@@ -2667,19 +2667,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G2">
-        <v>17.39</v>
+        <v>4.35</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -2699,30 +2699,30 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>46</v>
@@ -2731,19 +2731,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G4">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2754,28 +2754,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="G5">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
@@ -2798,27 +2798,27 @@
         <v>22</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>95.65000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
@@ -2827,19 +2827,19 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2855,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2880,66 +2880,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920145</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920145</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2975,47 +2915,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920145</v>
+        <v>19330051920125</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
         <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920140</v>
+        <v>19330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920125</v>
+        <v>19330051920127</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
         <v>91</v>
@@ -3026,13 +2966,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920126</v>
+        <v>19330051920128</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
         <v>92</v>
@@ -3043,13 +2983,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920127</v>
+        <v>19330051920129</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -3060,13 +3000,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920128</v>
+        <v>19330051920130</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
         <v>94</v>
@@ -3077,13 +3017,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920129</v>
+        <v>19330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>95</v>
@@ -3094,13 +3034,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920130</v>
+        <v>19330051920131</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>96</v>
@@ -3111,13 +3051,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920380</v>
+        <v>19330051920132</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>97</v>
@@ -3128,13 +3068,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920131</v>
+        <v>19330051920133</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>98</v>
@@ -3145,13 +3085,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920132</v>
+        <v>19330051920134</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
         <v>99</v>
@@ -3162,13 +3102,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920133</v>
+        <v>19330051920135</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -3179,13 +3119,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920134</v>
+        <v>19330051920002</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
         <v>101</v>
@@ -3196,13 +3136,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920135</v>
+        <v>19330051920136</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>102</v>
@@ -3213,13 +3153,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920002</v>
+        <v>19330051920137</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>103</v>
@@ -3230,13 +3170,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920136</v>
+        <v>19330051920140</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>104</v>
@@ -3247,13 +3187,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920137</v>
+        <v>19330051920139</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>105</v>
@@ -3264,13 +3204,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920139</v>
+        <v>19330051920143</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>106</v>
@@ -3281,13 +3221,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920143</v>
+        <v>19330051920141</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>107</v>
@@ -3298,13 +3238,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920141</v>
+        <v>19330051920144</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>108</v>
@@ -3315,13 +3255,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920144</v>
+        <v>19330051920145</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -3335,10 +3275,10 @@
         <v>19330051920147</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
         <v>110</v>
@@ -3352,10 +3292,10 @@
         <v>19330051920431</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>111</v>
@@ -3371,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3401,144 +3341,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920130</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920140</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920140</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920139</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920431</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
